--- a/artfynd/A 25511-2026 artfynd.xlsx
+++ b/artfynd/A 25511-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117990580</v>
+        <v>117990628</v>
       </c>
       <c r="B2" t="n">
-        <v>97880</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mullebovägen lokal2, Hofors, Gstr</t>
+          <t>Mullebovägen lokal 3, Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572478</v>
+        <v>572569</v>
       </c>
       <c r="R2" t="n">
-        <v>6708148</v>
+        <v>6707983</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -794,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126584023</v>
+        <v>117990717</v>
       </c>
       <c r="B3" t="n">
-        <v>98476</v>
+        <v>99142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,26 +800,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,17 +836,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mullebovägen, Hofors, Gstr</t>
+          <t>Mullebovägen, lokal 4, Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572492</v>
+        <v>572585</v>
       </c>
       <c r="R3" t="n">
-        <v>6708162</v>
+        <v>6707979</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,6 +900,340 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127054804</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lilla Torstjärnen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>572573</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6707974</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>117990580</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mullebovägen lokal2, Hofors, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>572478</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6708148</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Barbro Risberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Barbro Risberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126584023</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mullebovägen, Hofors, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>572492</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6708162</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Barbro Risberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Barbro Risberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25511-2026 artfynd.xlsx
+++ b/artfynd/A 25511-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117990628</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117990717</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127054804</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117990580</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,8 +1259,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126584023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>